--- a/utils/monday_sprint_sprint_2023-19.xlsx
+++ b/utils/monday_sprint_sprint_2023-19.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="652" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="651" uniqueCount="154">
   <si>
     <t>Ticket</t>
   </si>
@@ -42,7 +42,7 @@
     <t>Equipe TI</t>
   </si>
   <si>
-    <t>Entrada Sprint</t>
+    <t>Abertura</t>
   </si>
   <si>
     <t>Encerramento</t>
@@ -51,7 +51,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>SLA (15 dias)</t>
+    <t>Dentro da SLA</t>
   </si>
   <si>
     <t>Semana</t>
@@ -60,7 +60,7 @@
     <t>Mês</t>
   </si>
   <si>
-    <t>22008</t>
+    <t>5053390952</t>
   </si>
   <si>
     <t>Setor não informado</t>
@@ -87,7 +87,7 @@
     <t>25/08/2023</t>
   </si>
   <si>
-    <t>N/A</t>
+    <t>13/09/2023</t>
   </si>
   <si>
     <t>Feito</t>
@@ -102,7 +102,7 @@
     <t>Agosto</t>
   </si>
   <si>
-    <t>19402</t>
+    <t>5078991905</t>
   </si>
   <si>
     <t>Relatório Razão Crítica &gt; Adequação do Lay Out</t>
@@ -111,10 +111,13 @@
     <t>30/08/2023</t>
   </si>
   <si>
+    <t>23/09/2023</t>
+  </si>
+  <si>
     <t>Semana 5</t>
   </si>
   <si>
-    <t>22006</t>
+    <t>5109377275</t>
   </si>
   <si>
     <t>Projeto</t>
@@ -129,13 +132,16 @@
     <t>05/09/2023</t>
   </si>
   <si>
+    <t>18/09/2023</t>
+  </si>
+  <si>
     <t>Semana 1</t>
   </si>
   <si>
     <t>Setembro</t>
   </si>
   <si>
-    <t>22197</t>
+    <t>5122174294</t>
   </si>
   <si>
     <t>Parametrização inicial CenciHUB (Implantação) - Altona SA</t>
@@ -144,13 +150,16 @@
     <t>07/09/2023</t>
   </si>
   <si>
-    <t>22196</t>
+    <t>11/09/2023</t>
+  </si>
+  <si>
+    <t>5122200494</t>
   </si>
   <si>
     <t>Dias de estoque</t>
   </si>
   <si>
-    <t>22195</t>
+    <t>5122228013</t>
   </si>
   <si>
     <t>Correção</t>
@@ -159,171 +168,201 @@
     <t>Erro no relatório de FUP</t>
   </si>
   <si>
-    <t>22184</t>
+    <t>5122256326</t>
   </si>
   <si>
     <t>Atribuição de mantenedor na OS</t>
   </si>
   <si>
-    <t>22174</t>
+    <t>5122736597</t>
   </si>
   <si>
     <t>Melhoria Relatório de Entrada de Notas Fiscais</t>
   </si>
   <si>
-    <t>22128</t>
+    <t>5122819204</t>
   </si>
   <si>
     <t>Botão Estoque (Pré Requisição)</t>
   </si>
   <si>
-    <t>22095</t>
+    <t>5122867166</t>
   </si>
   <si>
     <t>Incluir coluna no relatório</t>
   </si>
   <si>
-    <t>22083</t>
+    <t>12/09/2023</t>
+  </si>
+  <si>
+    <t>5122915356</t>
   </si>
   <si>
     <t>Alterar Sistema - Consulta etiquetas</t>
   </si>
   <si>
-    <t>22039</t>
+    <t>5122965849</t>
   </si>
   <si>
     <t>Agrupar os inventários - Expedição</t>
   </si>
   <si>
-    <t>22022</t>
+    <t>5123003610</t>
   </si>
   <si>
     <t>Alterar local do cursor</t>
   </si>
   <si>
-    <t>22004</t>
+    <t>5123051075</t>
   </si>
   <si>
     <t>Inclusão de Segmentação relatório de Cte</t>
   </si>
   <si>
-    <t>21490</t>
+    <t>5123084179</t>
   </si>
   <si>
     <t>PROJETO FATURA - Criar nível de prazo nas FTFs por oferta</t>
   </si>
   <si>
-    <t>21373</t>
+    <t>17/09/2023</t>
+  </si>
+  <si>
+    <t>5123095811</t>
   </si>
   <si>
     <t>Programação moldagem - Itens não liberados e não programados</t>
   </si>
   <si>
-    <t>20717</t>
+    <t>5123116989</t>
   </si>
   <si>
     <t>Acesso ao Bancos de Dados</t>
   </si>
   <si>
-    <t>19219</t>
+    <t>14/09/2023</t>
+  </si>
+  <si>
+    <t>5123229574</t>
   </si>
   <si>
     <t>Melhoria Atualização diária das saídas</t>
   </si>
   <si>
-    <t>22103</t>
+    <t>20/09/2023</t>
+  </si>
+  <si>
+    <t>5125408464</t>
   </si>
   <si>
     <t>Posto de cópia eletronico</t>
   </si>
   <si>
-    <t>22014</t>
+    <t>5125351912</t>
   </si>
   <si>
     <t>Integração NIMBI x ERP Altona</t>
   </si>
   <si>
+    <t>24/09/2023</t>
+  </si>
+  <si>
     <t>A fazer</t>
   </si>
   <si>
-    <t>Aberto</t>
-  </si>
-  <si>
-    <t>21877</t>
+    <t>5053980380</t>
   </si>
   <si>
     <t>SISTEMA DE O.S. PARA FERRAMENTARIA DA USINAGEM</t>
   </si>
   <si>
-    <t>22101</t>
+    <t>21/09/2023</t>
+  </si>
+  <si>
+    <t>5122836747</t>
   </si>
   <si>
     <t>Acesso documentos</t>
   </si>
   <si>
-    <t>22091</t>
+    <t>19/09/2023</t>
+  </si>
+  <si>
+    <t>5122880300</t>
   </si>
   <si>
     <t>Alerta na SIC</t>
   </si>
   <si>
-    <t>22084</t>
+    <t>5122900999</t>
   </si>
   <si>
     <t>SUPRIMENTOS] Melhoria as telas de Material e Fornecedor</t>
   </si>
   <si>
-    <t>22079</t>
+    <t>5122923977</t>
   </si>
   <si>
     <t>Sistema CPP não replica arquivos quando copiado</t>
   </si>
   <si>
-    <t>22057</t>
+    <t>5122948226</t>
   </si>
   <si>
     <t>Unificação Sistema PID, MPO e Checklist</t>
   </si>
   <si>
-    <t>19155</t>
+    <t>5124063030</t>
   </si>
   <si>
     <t>Serviços em Terceiros na Carteira QlikView</t>
   </si>
   <si>
-    <t>6090</t>
+    <t>5125222314</t>
   </si>
   <si>
     <t>Novo sistema revisão de documentos (Analise)</t>
   </si>
   <si>
-    <t>18941</t>
+    <t>5125260298</t>
   </si>
   <si>
     <t>Produtivo em horas</t>
   </si>
   <si>
-    <t>21214</t>
+    <t>5141363242</t>
   </si>
   <si>
     <t>Cadastro de questionário pela engenharia, vinculado ao modelo</t>
   </si>
   <si>
-    <t>11/09/2023</t>
-  </si>
-  <si>
     <t>Semana 2</t>
   </si>
   <si>
+    <t>5141370052</t>
+  </si>
+  <si>
     <t>Opção para importar planilha atual de PDI ( Seq, descrição da dimensão, instrumento, Freq, Tipo (cota ou ok/nok), cota min, cota máx)</t>
   </si>
   <si>
+    <t>5141371613</t>
+  </si>
+  <si>
     <t>Tela de abertura do PDI e informação das sequencias (no máximo 10). Permitir até 2 modelos e demais campos do cabeçalho conforme formulário</t>
   </si>
   <si>
+    <t>22/09/2023</t>
+  </si>
+  <si>
+    <t>5141372898</t>
+  </si>
+  <si>
     <t>Tela para inspeção e informação das cotas e aprovados/reprovados</t>
   </si>
   <si>
+    <t>5141378055</t>
+  </si>
+  <si>
     <t>Tela para apontar inspeção de itens reprovados</t>
   </si>
   <si>
@@ -351,7 +390,7 @@
     <t>Período</t>
   </si>
   <si>
-    <t>SPRINT 2023-19</t>
+    <t>Ago/2023</t>
   </si>
   <si>
     <t>Base</t>
@@ -406,6 +445,9 @@
   </si>
   <si>
     <t>Sim</t>
+  </si>
+  <si>
+    <t>Semana 3</t>
   </si>
   <si>
     <t>Abertos</t>
@@ -993,7 +1035,7 @@
         <v>31</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="L3" s="2" t="s">
         <v>25</v>
@@ -1002,7 +1044,7 @@
         <v>26</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O3" s="2" t="s">
         <v>28</v>
@@ -1010,25 +1052,25 @@
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H4" s="2" t="s">
         <v>21</v>
@@ -1037,10 +1079,10 @@
         <v>22</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="L4" s="2" t="s">
         <v>25</v>
@@ -1049,30 +1091,30 @@
         <v>26</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="O4" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>20</v>
@@ -1084,10 +1126,10 @@
         <v>22</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>24</v>
+        <v>45</v>
       </c>
       <c r="L5" s="2" t="s">
         <v>25</v>
@@ -1096,15 +1138,15 @@
         <v>26</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="O5" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>16</v>
@@ -1116,10 +1158,10 @@
         <v>18</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>20</v>
@@ -1131,7 +1173,7 @@
         <v>22</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="K6" s="2" t="s">
         <v>24</v>
@@ -1143,30 +1185,30 @@
         <v>26</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="O6" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>20</v>
@@ -1178,7 +1220,7 @@
         <v>22</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="K7" s="2" t="s">
         <v>24</v>
@@ -1190,15 +1232,15 @@
         <v>26</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="O7" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>16</v>
@@ -1210,10 +1252,10 @@
         <v>18</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>20</v>
@@ -1225,10 +1267,10 @@
         <v>22</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="L8" s="2" t="s">
         <v>25</v>
@@ -1237,15 +1279,15 @@
         <v>26</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="O8" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>16</v>
@@ -1257,10 +1299,10 @@
         <v>18</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>20</v>
@@ -1272,7 +1314,7 @@
         <v>22</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="K9" s="2" t="s">
         <v>24</v>
@@ -1284,15 +1326,15 @@
         <v>26</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="O9" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>16</v>
@@ -1304,10 +1346,10 @@
         <v>18</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>20</v>
@@ -1319,10 +1361,10 @@
         <v>22</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="L10" s="2" t="s">
         <v>25</v>
@@ -1331,15 +1373,15 @@
         <v>26</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="O10" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>16</v>
@@ -1351,10 +1393,10 @@
         <v>18</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>20</v>
@@ -1366,10 +1408,10 @@
         <v>22</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>24</v>
+        <v>59</v>
       </c>
       <c r="L11" s="2" t="s">
         <v>25</v>
@@ -1378,15 +1420,15 @@
         <v>26</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="O11" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>16</v>
@@ -1398,10 +1440,10 @@
         <v>18</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>20</v>
@@ -1413,10 +1455,10 @@
         <v>22</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="L12" s="2" t="s">
         <v>25</v>
@@ -1425,15 +1467,15 @@
         <v>26</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="O12" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>16</v>
@@ -1445,10 +1487,10 @@
         <v>18</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>20</v>
@@ -1460,10 +1502,10 @@
         <v>22</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>24</v>
+        <v>59</v>
       </c>
       <c r="L13" s="2" t="s">
         <v>25</v>
@@ -1472,15 +1514,15 @@
         <v>26</v>
       </c>
       <c r="N13" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="O13" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>16</v>
@@ -1492,10 +1534,10 @@
         <v>18</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>20</v>
@@ -1507,10 +1549,10 @@
         <v>22</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="L14" s="2" t="s">
         <v>25</v>
@@ -1519,15 +1561,15 @@
         <v>26</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="O14" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>16</v>
@@ -1539,10 +1581,10 @@
         <v>18</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>20</v>
@@ -1554,10 +1596,10 @@
         <v>22</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>24</v>
+        <v>59</v>
       </c>
       <c r="L15" s="2" t="s">
         <v>25</v>
@@ -1566,30 +1608,30 @@
         <v>26</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="O15" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>20</v>
@@ -1601,10 +1643,10 @@
         <v>22</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>24</v>
+        <v>70</v>
       </c>
       <c r="L16" s="2" t="s">
         <v>25</v>
@@ -1613,15 +1655,15 @@
         <v>26</v>
       </c>
       <c r="N16" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="O16" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>16</v>
@@ -1633,10 +1675,10 @@
         <v>18</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>20</v>
@@ -1648,10 +1690,10 @@
         <v>22</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="L17" s="2" t="s">
         <v>25</v>
@@ -1660,15 +1702,15 @@
         <v>26</v>
       </c>
       <c r="N17" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="O17" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>16</v>
@@ -1680,10 +1722,10 @@
         <v>18</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>20</v>
@@ -1695,10 +1737,10 @@
         <v>22</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>24</v>
+        <v>75</v>
       </c>
       <c r="L18" s="2" t="s">
         <v>25</v>
@@ -1707,15 +1749,15 @@
         <v>26</v>
       </c>
       <c r="N18" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="O18" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>16</v>
@@ -1727,10 +1769,10 @@
         <v>18</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>20</v>
@@ -1742,10 +1784,10 @@
         <v>22</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>24</v>
+        <v>78</v>
       </c>
       <c r="L19" s="2" t="s">
         <v>25</v>
@@ -1754,30 +1796,30 @@
         <v>26</v>
       </c>
       <c r="N19" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="O19" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>20</v>
@@ -1789,10 +1831,10 @@
         <v>22</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="L20" s="2" t="s">
         <v>25</v>
@@ -1801,33 +1843,33 @@
         <v>26</v>
       </c>
       <c r="N20" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="O20" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H21" s="2" t="s">
         <v>21</v>
@@ -1836,27 +1878,27 @@
         <v>22</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>24</v>
+        <v>83</v>
       </c>
       <c r="L21" s="2" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="M21" s="2" t="s">
-        <v>77</v>
+        <v>26</v>
       </c>
       <c r="N21" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="O21" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>16</v>
@@ -1868,10 +1910,10 @@
         <v>18</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>20</v>
@@ -1886,7 +1928,7 @@
         <v>23</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>24</v>
+        <v>87</v>
       </c>
       <c r="L22" s="2" t="s">
         <v>25</v>
@@ -1903,7 +1945,7 @@
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>16</v>
@@ -1915,10 +1957,10 @@
         <v>18</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>20</v>
@@ -1930,10 +1972,10 @@
         <v>22</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>24</v>
+        <v>90</v>
       </c>
       <c r="L23" s="2" t="s">
         <v>25</v>
@@ -1942,15 +1984,15 @@
         <v>26</v>
       </c>
       <c r="N23" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="O23" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>16</v>
@@ -1962,10 +2004,10 @@
         <v>18</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>20</v>
@@ -1977,10 +2019,10 @@
         <v>22</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>24</v>
+        <v>87</v>
       </c>
       <c r="L24" s="2" t="s">
         <v>25</v>
@@ -1989,15 +2031,15 @@
         <v>26</v>
       </c>
       <c r="N24" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="O24" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>84</v>
+        <v>93</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>16</v>
@@ -2009,10 +2051,10 @@
         <v>18</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>20</v>
@@ -2024,10 +2066,10 @@
         <v>22</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="L25" s="2" t="s">
         <v>25</v>
@@ -2036,30 +2078,30 @@
         <v>26</v>
       </c>
       <c r="N25" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="O25" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="G26" s="2" t="s">
         <v>20</v>
@@ -2071,10 +2113,10 @@
         <v>22</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="K26" s="2" t="s">
-        <v>24</v>
+        <v>87</v>
       </c>
       <c r="L26" s="2" t="s">
         <v>25</v>
@@ -2083,15 +2125,15 @@
         <v>26</v>
       </c>
       <c r="N26" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="O26" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>88</v>
+        <v>97</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>16</v>
@@ -2103,10 +2145,10 @@
         <v>18</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>89</v>
+        <v>98</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>89</v>
+        <v>98</v>
       </c>
       <c r="G27" s="2" t="s">
         <v>20</v>
@@ -2118,10 +2160,10 @@
         <v>22</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="K27" s="2" t="s">
-        <v>24</v>
+        <v>90</v>
       </c>
       <c r="L27" s="2" t="s">
         <v>25</v>
@@ -2130,15 +2172,15 @@
         <v>26</v>
       </c>
       <c r="N27" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="O27" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>16</v>
@@ -2150,10 +2192,10 @@
         <v>18</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="G28" s="2" t="s">
         <v>20</v>
@@ -2165,10 +2207,10 @@
         <v>22</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>24</v>
+        <v>75</v>
       </c>
       <c r="L28" s="2" t="s">
         <v>25</v>
@@ -2177,15 +2219,15 @@
         <v>26</v>
       </c>
       <c r="N28" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="O28" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>16</v>
@@ -2197,10 +2239,10 @@
         <v>18</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>93</v>
+        <v>102</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>93</v>
+        <v>102</v>
       </c>
       <c r="G29" s="2" t="s">
         <v>20</v>
@@ -2212,10 +2254,10 @@
         <v>22</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="K29" s="2" t="s">
-        <v>24</v>
+        <v>87</v>
       </c>
       <c r="L29" s="2" t="s">
         <v>25</v>
@@ -2224,33 +2266,33 @@
         <v>26</v>
       </c>
       <c r="N29" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="O29" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D30" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H30" s="2" t="s">
         <v>21</v>
@@ -2259,10 +2301,10 @@
         <v>22</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="K30" s="2" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="L30" s="2" t="s">
         <v>25</v>
@@ -2271,30 +2313,30 @@
         <v>26</v>
       </c>
       <c r="N30" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="O30" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D31" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>97</v>
+        <v>106</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>97</v>
+        <v>106</v>
       </c>
       <c r="G31" s="2" t="s">
         <v>20</v>
@@ -2306,10 +2348,10 @@
         <v>22</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>98</v>
+        <v>45</v>
       </c>
       <c r="K31" s="2" t="s">
-        <v>24</v>
+        <v>90</v>
       </c>
       <c r="L31" s="2" t="s">
         <v>25</v>
@@ -2318,30 +2360,30 @@
         <v>26</v>
       </c>
       <c r="N31" s="2" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="O31" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>96</v>
+        <v>108</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D32" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>100</v>
+        <v>109</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>100</v>
+        <v>109</v>
       </c>
       <c r="G32" s="2" t="s">
         <v>20</v>
@@ -2353,10 +2395,10 @@
         <v>22</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>98</v>
+        <v>45</v>
       </c>
       <c r="K32" s="2" t="s">
-        <v>24</v>
+        <v>90</v>
       </c>
       <c r="L32" s="2" t="s">
         <v>25</v>
@@ -2365,30 +2407,30 @@
         <v>26</v>
       </c>
       <c r="N32" s="2" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="O32" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D33" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="G33" s="2" t="s">
         <v>20</v>
@@ -2400,10 +2442,10 @@
         <v>22</v>
       </c>
       <c r="J33" s="2" t="s">
-        <v>98</v>
+        <v>45</v>
       </c>
       <c r="K33" s="2" t="s">
-        <v>24</v>
+        <v>112</v>
       </c>
       <c r="L33" s="2" t="s">
         <v>25</v>
@@ -2412,30 +2454,30 @@
         <v>26</v>
       </c>
       <c r="N33" s="2" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="O33" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>96</v>
+        <v>113</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D34" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="G34" s="2" t="s">
         <v>20</v>
@@ -2447,10 +2489,10 @@
         <v>22</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>98</v>
+        <v>45</v>
       </c>
       <c r="K34" s="2" t="s">
-        <v>24</v>
+        <v>112</v>
       </c>
       <c r="L34" s="2" t="s">
         <v>25</v>
@@ -2459,30 +2501,30 @@
         <v>26</v>
       </c>
       <c r="N34" s="2" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="O34" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>96</v>
+        <v>115</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D35" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>103</v>
+        <v>116</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>103</v>
+        <v>116</v>
       </c>
       <c r="G35" s="2" t="s">
         <v>20</v>
@@ -2494,10 +2536,10 @@
         <v>22</v>
       </c>
       <c r="J35" s="2" t="s">
-        <v>98</v>
+        <v>45</v>
       </c>
       <c r="K35" s="2" t="s">
-        <v>24</v>
+        <v>112</v>
       </c>
       <c r="L35" s="2" t="s">
         <v>25</v>
@@ -2506,151 +2548,151 @@
         <v>26</v>
       </c>
       <c r="N35" s="2" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="O35" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>104</v>
+        <v>117</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>105</v>
+        <v>118</v>
       </c>
       <c r="D36" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>106</v>
+        <v>119</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>106</v>
+        <v>119</v>
       </c>
       <c r="G36" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="H36" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I36" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J36" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="K36" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="L36" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M36" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="N36" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="H36" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="I36" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="J36" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="K36" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="L36" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="M36" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="N36" s="2" t="s">
-        <v>99</v>
-      </c>
       <c r="O36" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>108</v>
+        <v>121</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>105</v>
+        <v>118</v>
       </c>
       <c r="D37" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>106</v>
+        <v>119</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>106</v>
+        <v>119</v>
       </c>
       <c r="G37" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="H37" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I37" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J37" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="K37" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="L37" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M37" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="N37" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="H37" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="I37" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="J37" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="K37" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="L37" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="M37" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="N37" s="2" t="s">
-        <v>99</v>
-      </c>
       <c r="O37" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>109</v>
+        <v>122</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>105</v>
+        <v>118</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>106</v>
+        <v>119</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>106</v>
+        <v>119</v>
       </c>
       <c r="G38" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="H38" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I38" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J38" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="K38" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="L38" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M38" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="N38" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="H38" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="I38" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="J38" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="K38" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="L38" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="M38" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="N38" s="2" t="s">
-        <v>99</v>
-      </c>
       <c r="O38" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
   </sheetData>
@@ -2666,23 +2708,23 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>110</v>
+        <v>123</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>111</v>
+        <v>124</v>
       </c>
       <c r="B2" t="s">
-        <v>112</v>
+        <v>125</v>
       </c>
       <c r="D2" t="s">
-        <v>113</v>
+        <v>126</v>
       </c>
       <c r="E2" t="s">
-        <v>114</v>
+        <v>127</v>
       </c>
       <c r="F2"/>
       <c r="G2"/>
@@ -2690,16 +2732,16 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>115</v>
+        <v>128</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>116</v>
+        <v>129</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>117</v>
+        <v>130</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>118</v>
+        <v>131</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -2710,7 +2752,7 @@
         <v>0</v>
       </c>
       <c r="G5" s="4">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="J5" s="4">
         <v>1</v>
@@ -2718,7 +2760,7 @@
     </row>
     <row r="21" spans="10:10" x14ac:dyDescent="0.25">
       <c r="J21" s="6" t="s">
-        <v>119</v>
+        <v>132</v>
       </c>
     </row>
     <row r="22" spans="10:11" x14ac:dyDescent="0.25">
@@ -2731,7 +2773,7 @@
     </row>
     <row r="23" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J23" t="s">
-        <v>120</v>
+        <v>133</v>
       </c>
       <c r="K23">
         <v>0</v>
@@ -2739,7 +2781,7 @@
     </row>
     <row r="24" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J24" t="s">
-        <v>121</v>
+        <v>134</v>
       </c>
       <c r="K24">
         <v>0</v>
@@ -2770,12 +2812,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>122</v>
+        <v>135</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>115</v>
+        <v>128</v>
       </c>
       <c r="B2">
         <v>37</v>
@@ -2789,7 +2831,7 @@
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>0</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
@@ -2799,25 +2841,25 @@
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>123</v>
+        <v>136</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>124</v>
+        <v>137</v>
       </c>
       <c r="G9" s="6" t="s">
         <v>6</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>125</v>
+        <v>138</v>
       </c>
       <c r="M9" s="6" t="s">
-        <v>126</v>
+        <v>139</v>
       </c>
       <c r="P9" s="6" t="s">
-        <v>127</v>
+        <v>140</v>
       </c>
       <c r="Q9" s="6" t="s">
-        <v>128</v>
+        <v>141</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
@@ -2834,13 +2876,13 @@
         <v>21</v>
       </c>
       <c r="G10" t="s">
-        <v>129</v>
+        <v>142</v>
       </c>
       <c r="H10">
         <v>0</v>
       </c>
       <c r="J10" t="s">
-        <v>130</v>
+        <v>143</v>
       </c>
       <c r="K10">
         <v>0</v>
@@ -2852,21 +2894,21 @@
         <v>36</v>
       </c>
       <c r="P10" t="s">
-        <v>38</v>
+        <v>107</v>
       </c>
       <c r="Q10">
-        <v>25</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D11" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E11">
         <v>11</v>
       </c>
       <c r="G11" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H11">
         <v>3</v>
@@ -2875,24 +2917,24 @@
         <v>26</v>
       </c>
       <c r="K11">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="M11" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="N11">
         <v>1</v>
       </c>
       <c r="P11" t="s">
-        <v>99</v>
+        <v>144</v>
       </c>
       <c r="Q11">
-        <v>8</v>
+        <v>16</v>
       </c>
     </row>
     <row r="12" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D12" t="s">
-        <v>105</v>
+        <v>118</v>
       </c>
       <c r="E12">
         <v>3</v>
@@ -2904,13 +2946,13 @@
         <v>31</v>
       </c>
       <c r="J12" t="s">
-        <v>131</v>
+        <v>145</v>
       </c>
       <c r="K12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M12" t="s">
-        <v>132</v>
+        <v>146</v>
       </c>
       <c r="N12">
         <v>0</v>
@@ -2919,44 +2961,38 @@
         <v>27</v>
       </c>
       <c r="Q12">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="13" spans="4:17" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13" spans="4:14" x14ac:dyDescent="0.25">
       <c r="D13" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="E13">
         <v>2</v>
       </c>
       <c r="G13" t="s">
-        <v>133</v>
+        <v>147</v>
       </c>
       <c r="H13">
         <v>0</v>
       </c>
       <c r="M13" t="s">
-        <v>134</v>
+        <v>148</v>
       </c>
       <c r="N13">
         <v>0</v>
       </c>
-      <c r="P13" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q13">
-        <v>1</v>
-      </c>
     </row>
     <row r="14" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G14" t="s">
-        <v>107</v>
+        <v>120</v>
       </c>
       <c r="H14">
         <v>3</v>
       </c>
       <c r="M14" t="s">
-        <v>120</v>
+        <v>133</v>
       </c>
       <c r="N14">
         <v>0</v>
@@ -2964,7 +3000,7 @@
     </row>
     <row r="15" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M15" t="s">
-        <v>135</v>
+        <v>149</v>
       </c>
       <c r="N15">
         <v>0</v>
@@ -2972,7 +3008,7 @@
     </row>
     <row r="16" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M16" t="s">
-        <v>136</v>
+        <v>150</v>
       </c>
       <c r="N16">
         <v>0</v>
@@ -2980,7 +3016,7 @@
     </row>
     <row r="17" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M17" t="s">
-        <v>137</v>
+        <v>151</v>
       </c>
       <c r="N17">
         <v>0</v>
@@ -2988,10 +3024,10 @@
     </row>
     <row r="19" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D19" s="6" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="20" ht="18" customHeight="1" spans="4:7" x14ac:dyDescent="0.25">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="20" spans="4:7" x14ac:dyDescent="0.25">
       <c r="D20" s="1" t="s">
         <v>0</v>
       </c>
@@ -2999,7 +3035,7 @@
         <v>1</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>139</v>
+        <v>153</v>
       </c>
       <c r="G20" s="1" t="s">
         <v>4</v>
@@ -3007,142 +3043,142 @@
     </row>
     <row r="21" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D21" s="2" t="s">
-        <v>15</v>
+        <v>81</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F21" s="2">
-        <v>0</v>
+        <v>1013</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>19</v>
+        <v>82</v>
       </c>
     </row>
     <row r="22" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D22" s="2" t="s">
-        <v>29</v>
+        <v>117</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F22" s="2">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>30</v>
+        <v>119</v>
       </c>
     </row>
     <row r="23" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D23" s="2" t="s">
-        <v>33</v>
+        <v>121</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F23" s="2">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>35</v>
+        <v>119</v>
       </c>
     </row>
     <row r="24" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D24" s="2" t="s">
-        <v>40</v>
+        <v>122</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F24" s="2">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>41</v>
+        <v>119</v>
       </c>
     </row>
     <row r="25" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D25" s="2" t="s">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F25" s="2">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>44</v>
+        <v>30</v>
       </c>
     </row>
     <row r="26" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D26" s="2" t="s">
-        <v>45</v>
+        <v>71</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F26" s="2">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>47</v>
+        <v>72</v>
       </c>
     </row>
     <row r="27" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D27" s="2" t="s">
-        <v>48</v>
+        <v>93</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F27" s="2">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>49</v>
+        <v>94</v>
       </c>
     </row>
     <row r="28" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D28" s="2" t="s">
-        <v>50</v>
+        <v>103</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F28" s="2">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>51</v>
+        <v>104</v>
       </c>
     </row>
     <row r="29" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D29" s="2" t="s">
-        <v>52</v>
+        <v>110</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F29" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>53</v>
+        <v>111</v>
       </c>
     </row>
     <row r="30" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D30" s="2" t="s">
-        <v>54</v>
+        <v>113</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F30" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>55</v>
+        <v>114</v>
       </c>
     </row>
   </sheetData>
